--- a/TA_FA_SA/code/v5/stock_trend/data_experiment_predict/df_news_official_stament.xlsx
+++ b/TA_FA_SA/code/v5/stock_trend/data_experiment_predict/df_news_official_stament.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31/07/2025 17:18</t>
+          <t>31/07/2025 00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://cafef.vn/du-lieu/VHM-2260054/vhm-bao-cao-tinh-hinh-quan-tri-6-thang-dau-nam-2025.chn</t>
+          <t>https://cafef.vn/du-lieu/VHM-2294765/vhm-bao-cao-tinh-hinh-quan-tri-6-thang-dau-nam-2025.chn?utm_source=du-lieu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
